--- a/XlsxSharp.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Automatic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lowest/Highest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Percent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Formula</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Percentile</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Automatic</t>
+  </si>
+  <si>
+    <t>Lowest/Highest</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Percentile</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -369,228 +369,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:F6"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:6">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="A5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
-      <x:c r="A6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:conditionalFormatting sqref="A2:A6">
-    <x:cfRule type="dataBar" priority="1">
-      <x:dataBar showValue="1">
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFFFBF00"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d30806a-f8bc-486c-b2cc-9391932bac5e}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="B2:B6">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar showValue="1">
-        <x:cfvo type="min" val="0"/>
-        <x:cfvo type="max" val="0"/>
-        <x:color rgb="FF21ABCD"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4c702ec-4f90-4f87-9d08-505c18166b58}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C2:C6">
-    <x:cfRule type="dataBar" priority="3">
-      <x:dataBar showValue="1">
-        <x:cfvo type="num" val="0"/>
-        <x:cfvo type="num" val="10"/>
-        <x:color rgb="FF536872"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cddaad48-b1b6-46a9-8ef3-330adecf7baa}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D2:D6">
-    <x:cfRule type="dataBar" priority="4">
-      <x:dataBar showValue="1">
-        <x:cfvo type="percent" val="50"/>
-        <x:cfvo type="percent" val="100"/>
-        <x:color rgb="FFC19A6B"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23068bd3-f630-47d0-9a83-01fbfff8e7e4}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E2:E6">
-    <x:cfRule type="dataBar" priority="5">
-      <x:dataBar showValue="1">
-        <x:cfvo type="formula" val="-SUM($A$2:$E$2)"/>
-        <x:cfvo type="formula" val="SUM($A$6:$E$6)"/>
-        <x:color rgb="FFC2B280"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed6d6dc8-01ec-425e-98c2-bd5aaef133b1}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F2:F6">
-    <x:cfRule type="dataBar" priority="6">
-      <x:dataBar showValue="1">
-        <x:cfvo type="percentile" val="30"/>
-        <x:cfvo type="percentile" val="70"/>
-        <x:color rgb="FFB53389"/>
-      </x:dataBar>
-      <x:extLst>
-        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{638c99e3-ba9d-49e5-84d6-7be58eaf1c9f}</x14:id>
-        </x:ext>
-      </x:extLst>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0">
+        <v>1</v>
+      </c>
+      <c r="F3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="0">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0">
+        <v>2</v>
+      </c>
+      <c r="C4" s="0">
+        <v>2</v>
+      </c>
+      <c r="D4" s="0">
+        <v>2</v>
+      </c>
+      <c r="E4" s="0">
+        <v>2</v>
+      </c>
+      <c r="F4" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="0">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0">
+        <v>3</v>
+      </c>
+      <c r="C5" s="0">
+        <v>3</v>
+      </c>
+      <c r="D5" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5" s="0">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="0">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0">
+        <v>4</v>
+      </c>
+      <c r="C6" s="0">
+        <v>4</v>
+      </c>
+      <c r="D6" s="0">
+        <v>4</v>
+      </c>
+      <c r="E6" s="0">
+        <v>4</v>
+      </c>
+      <c r="F6" s="0">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A6">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFBF00"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{fbd060a1-a99e-420f-89d0-7d6d6aec495b}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B6">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1">
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF21ABCD"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{73e3d21d-2afe-456b-aa26-34c5a36f64b5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C6">
+    <cfRule type="dataBar" priority="3">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FF536872"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{c90cddea-d543-42eb-a0af-f96cab182b0c}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D6">
+    <cfRule type="dataBar" priority="4">
+      <dataBar showValue="1">
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FFC19A6B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{a53b59ea-cd01-40d6-9ac7-497f42de500a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E6">
+    <cfRule type="dataBar" priority="5">
+      <dataBar showValue="1">
+        <cfvo type="formula" val="-SUM($A$2:$E$2)"/>
+        <cfvo type="formula" val="SUM($A$6:$E$6)"/>
+        <color rgb="FFC2B280"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{bf807b0a-87b9-4d41-a5c3-bbfa3781db05}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="dataBar" priority="6">
+      <dataBar showValue="1">
+        <cfvo type="percentile" val="30"/>
+        <cfvo type="percentile" val="70"/>
+        <color rgb="FFB53389"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{fd3661bb-5966-4258-b624-d156ef3b61dd}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d30806a-f8bc-486c-b2cc-9391932bac5e}">
+          <x14:cfRule type="dataBar" id="{fbd060a1-a99e-420f-89d0-7d6d6aec495b}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -601,7 +601,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4c702ec-4f90-4f87-9d08-505c18166b58}">
+          <x14:cfRule type="dataBar" id="{73e3d21d-2afe-456b-aa26-34c5a36f64b5}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -616,7 +616,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cddaad48-b1b6-46a9-8ef3-330adecf7baa}">
+          <x14:cfRule type="dataBar" id="{c90cddea-d543-42eb-a0af-f96cab182b0c}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -631,7 +631,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23068bd3-f630-47d0-9a83-01fbfff8e7e4}">
+          <x14:cfRule type="dataBar" id="{a53b59ea-cd01-40d6-9ac7-497f42de500a}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -646,7 +646,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ed6d6dc8-01ec-425e-98c2-bd5aaef133b1}">
+          <x14:cfRule type="dataBar" id="{bf807b0a-87b9-4d41-a5c3-bbfa3781db05}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -661,7 +661,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{638c99e3-ba9d-49e5-84d6-7be58eaf1c9f}">
+          <x14:cfRule type="dataBar" id="{fd3661bb-5966-4258-b624-d156ef3b61dd}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>
@@ -676,7 +676,7 @@
           <xm:sqref>F2:F6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
-    </x:ext>
-  </x:extLst>
-</x:worksheet>
+    </ext>
+  </extLst>
+</worksheet>
 </file>